--- a/solution_summary.xlsx
+++ b/solution_summary.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$P$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -628,12 +628,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_1_GREEDY_20260602_215616</t>
+          <t>RmediumCmany_1_GREEDY_20260608_094811</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_1</t>
+          <t>RmediumCmany_1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -647,16 +647,16 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="6" t="n">
-        <v>68.01790670547619</v>
+        <v>78.64211741666665</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>60.01790670547619</v>
+        <v>70.64211741666665</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.0168751000019256</v>
+        <v>0.03977869998198003</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>0</v>
@@ -680,12 +680,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_1_LA_S50_H24_20260603_111343</t>
+          <t>RmediumCmany_1_LA_S50_H24_20260607_233038</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_1</t>
+          <t>RmediumCmany_1</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="I3" s="12" t="n">
-        <v>63.10821947203578</v>
+        <v>73.05906345584502</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>55.10821947203578</v>
+        <v>65.05906345584502</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>1967.448479499988</v>
+        <v>3321.823949500103</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="M3" s="13" t="n">
         <v>0</v>
@@ -746,12 +746,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_1_RO_d20_G38_20260603_103958</t>
+          <t>RmediumCmany_1_RO_d40_G43_20260608_090500</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_1</t>
+          <t>RmediumCmany_1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -762,21 +762,21 @@
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="6" t="n">
-        <v>62.9692177532143</v>
+        <v>76.41137761636904</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>54.9692177532143</v>
+        <v>68.41137761636904</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>951.6673869000224</v>
+        <v>2174.727103000041</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>0</v>
@@ -798,105 +798,55 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>RmediumCfew_2_LA_S50_H24_20260603_114846</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>RmediumCfew_2</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>lp</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>53.69313401002289</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>45.69313401002289</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>1161.543855099997</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>51.48587519856191</v>
-      </c>
-      <c r="M5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
+      <c r="A5" s="8" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_2_RO_d20_G28_20260603_105653</t>
+          <t>RmediumCmany_2_GREEDY_20260607_184204</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_2</t>
+          <t>RmediumCmany_2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="5" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="6" t="n">
-        <v>53.39816867726203</v>
+        <v>59.10586954714285</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>45.39816867726203</v>
+        <v>51.10586954714285</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>607.4437424999778</v>
+        <v>0.01340890000574291</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>0</v>
@@ -920,12 +870,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_3_LA_S50_H24_20260603_120829</t>
+          <t>RmediumCmany_2_LA_S50_H24_20260607_112146</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_3</t>
+          <t>RmediumCmany_2</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -940,7 +890,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
@@ -953,16 +903,16 @@
         </is>
       </c>
       <c r="I7" s="12" t="n">
-        <v>63.11641118745051</v>
+        <v>54.66108585110236</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>55.11641118745051</v>
+        <v>46.66108585110236</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>1755.691028299974</v>
+        <v>3081.364407100016</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>60.63537464247023</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0</v>
@@ -986,12 +936,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_3_RO_d20_G38_20260603_101311</t>
+          <t>RmediumCmany_2_RO_d40_G32_20260607_183504</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RmediumCfew_3</t>
+          <t>RmediumCmany_2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1002,21 +952,21 @@
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="6" t="n">
-        <v>63.12365596635378</v>
+        <v>57.38998875480632</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>55.12365596635378</v>
+        <v>49.38998875480632</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>846.7393692000187</v>
+        <v>397.9649376999587</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>60.63537464247023</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>0</v>
@@ -1040,12 +990,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_10_GREEDY_20260603_093259</t>
+          <t>RmediumCmany_3_GREEDY_20260607_204053</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_10</t>
+          <t>RmediumCmany_3</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1059,16 +1009,16 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="12" t="n">
-        <v>34.30662940714284</v>
+        <v>71.54532548023808</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>26.30662940714284</v>
+        <v>63.54532548023808</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.009606400009943172</v>
+        <v>0.0257422000868246</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>30.79847871857142</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0</v>
@@ -1092,35 +1042,49 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_1_GREEDY_20260602_215250</t>
+          <t>RmediumCmany_3_LA_S50_H24_20260607_184225</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>greedy</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n">
-        <v>39.6625499595238</v>
+        <v>63.91878390299888</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>31.6625499595238</v>
+        <v>55.91878390299888</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.01212499999382999</v>
+        <v>3355.085748899961</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>0</v>
@@ -1144,49 +1108,37 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_1_LA_S100_H24_20260603_093336</t>
+          <t>RmediumCmany_3_RO_d40_G43_20260607_211555</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_3</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>24</v>
-      </c>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>lp</t>
-        </is>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="12" t="n">
-        <v>36.86501604614607</v>
+        <v>66.969462261356</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>28.86501604614607</v>
+        <v>58.969462261356</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>1327.334897199995</v>
+        <v>576.6021185000427</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0</v>
@@ -1210,49 +1162,35 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_1_LA_S50_H24_20260602_213851</t>
+          <t>RmediumCmany_4_GREEDY_20260607_214024</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_4</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>lp</t>
-        </is>
-      </c>
+          <t>greedy</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="6" t="n">
-        <v>37.11218263385243</v>
+        <v>64.91336019095237</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>29.11218263385243</v>
+        <v>56.91336019095237</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>771.1974623000133</v>
+        <v>0.03449240000918508</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>34.8281524437711</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>0</v>
@@ -1276,37 +1214,49 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_1_RO_d20_G20_20260603_101105</t>
+          <t>RmediumCmany_4_LA_S50_H24_20260607_221607</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_4</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="10" t="n"/>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>24</v>
+      </c>
       <c r="F13" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
       <c r="I13" s="12" t="n">
-        <v>35.96842184845237</v>
+        <v>59.60065254168538</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>27.96842184845237</v>
+        <v>51.60065254168538</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>28.79830379999476</v>
+        <v>4383.776991799939</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>34.8281524437711</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0</v>
@@ -1330,35 +1280,37 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_2_GREEDY_20260602_215259</t>
+          <t>RmediumCmany_4_RO_d40_G38_20260607_220806</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_2</t>
+          <t>RmediumCmany_4</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="F14" s="5" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="6" t="n">
-        <v>33.87595654499999</v>
+        <v>62.25175325416657</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>25.87595654499999</v>
+        <v>54.25175325416657</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.009485100003075786</v>
+        <v>444.1134314999217</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>30.61323638288689</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>0</v>
@@ -1382,37 +1334,35 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_2_RO_d20_G16_20260603_101143</t>
+          <t>RshortCmedium_1_GREEDY_20260608_095123</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_2</t>
+          <t>RshortCmedium_1</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="11" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="12" t="n">
-        <v>31.75477415523805</v>
+        <v>39.54358346047619</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>23.75477415523805</v>
+        <v>31.54358346047619</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>18.58239659998799</v>
+        <v>0.01416389993391931</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>30.61323638288689</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0</v>
@@ -1436,35 +1386,49 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_3_GREEDY_20260602_215338</t>
+          <t>RshortCmedium_1_LA_S50_H24_20260608_101622</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_3</t>
+          <t>RshortCmedium_1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>greedy</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n">
-        <v>38.58447148000001</v>
+        <v>37.157255159599</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>30.58447148000001</v>
+        <v>29.157255159599</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.01140050000685733</v>
+        <v>1734.567650500103</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
@@ -1488,12 +1452,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_3_RO_d20_G20_20260603_101227</t>
+          <t>RshortCmedium_1_RO_d40_G22_20260608_095947</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_3</t>
+          <t>RshortCmedium_1</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1504,21 +1468,21 @@
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="12" t="n">
-        <v>35.78658326035708</v>
+        <v>38.12381854774306</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>27.78658326035708</v>
+        <v>30.12381854774306</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>18.77433230000315</v>
+        <v>34.33920040004887</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0</v>
@@ -1542,12 +1506,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_4_GREEDY_20260603_092932</t>
+          <t>RshortCmedium_2_GREEDY_20260608_111232</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_4</t>
+          <t>RshortCmedium_2</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1561,16 +1525,16 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="6" t="n">
-        <v>34.0275978452381</v>
+        <v>34.44657884523808</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>26.0275978452381</v>
+        <v>26.44657884523808</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.008480099990265444</v>
+        <v>0.009670100058428943</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.64735112160713</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>0</v>
@@ -1594,35 +1558,49 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_5_GREEDY_20260603_093009</t>
+          <t>RshortCmedium_2_LA_S50_H24_20260608_104903</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_5</t>
+          <t>RshortCmedium_2</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>greedy</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
       <c r="I19" s="12" t="n">
-        <v>35.81904773809524</v>
+        <v>32.15800254512007</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>27.81904773809524</v>
+        <v>24.15800254512007</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.01075739998486824</v>
+        <v>1081.32966040005</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>32.32325378330357</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0</v>
@@ -1646,35 +1624,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_6_GREEDY_20260603_093109</t>
+          <t>RshortCmedium_2_RO_d40_G18_20260608_100856</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_6</t>
+          <t>RshortCmedium_2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="5" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="6" t="n">
-        <v>34.70600726309525</v>
+        <v>33.78295101238334</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>26.70600726309525</v>
+        <v>25.78295101238334</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.01008800001000054</v>
+        <v>50.17407589999493</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>31.95230189241174</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>0</v>
@@ -1698,12 +1678,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_7_GREEDY_20260603_093128</t>
+          <t>RshortCmedium_3_GREEDY_20260608_124706</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_7</t>
+          <t>RshortCmedium_3</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1717,16 +1697,16 @@
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="12" t="n">
-        <v>34.33002832380952</v>
+        <v>39.62859034047619</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>26.33002832380952</v>
+        <v>31.62859034047619</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.009918800002196804</v>
+        <v>0.01073680003173649</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>31.0660137785119</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>0</v>
@@ -1750,35 +1730,49 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_8_GREEDY_20260603_093158</t>
+          <t>RshortCmedium_3_LA_S50_H24_20260608_111246</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RshortCfew_8</t>
+          <t>RshortCmedium_3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>greedy</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n">
-        <v>34.47965599142857</v>
+        <v>36.31502266666667</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>26.47965599142857</v>
+        <v>28.31502266666667</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.009534300013910979</v>
+        <v>1599.284851899953</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>32.43163137910714</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>0</v>
@@ -1802,35 +1796,37 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_9_GREEDY_20260603_093225</t>
+          <t>RshortCmedium_3_RO_d40_G22_20260608_124305</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_9</t>
+          <t>RshortCmedium_3</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="10" t="n"/>
-      <c r="F23" s="11" t="n"/>
+      <c r="F23" s="11" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="8" t="inlineStr"/>
       <c r="I23" s="12" t="n">
-        <v>38.67555929238095</v>
+        <v>38.26393734589607</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>30.67555929238095</v>
+        <v>30.26393734589607</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.00960369998938404</v>
+        <v>63.51679699996021</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>34.89256813824403</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0</v>
@@ -1852,58 +1848,176 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4_GREEDY_20260608_124627</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>greedy</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="I24" s="6" t="n">
+        <v>35.46977987</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>27.46977987</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.01438190008047968</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr"/>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="8" t="inlineStr"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr"/>
-      <c r="P25" s="8" t="inlineStr"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4_LA_S50_H24_20260608_114507</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>33.63751991845975</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>25.63751991845975</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>1098.845269000041</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4_RO_d40_G19_20260608_124538</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="4" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="F26" s="5" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="I26" s="6" t="n">
+        <v>35.33904522678572</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>27.33904522678572</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>31.2397441000212</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr"/>
@@ -2049,44 +2163,8 @@
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr"/>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="13" t="n"/>
-      <c r="N35" s="8" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr"/>
-      <c r="P35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="6" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P36"/>
+  <autoFilter ref="A1:P34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2097,7 +2175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2176,7 +2254,7 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" s="17" t="n"/>
       <c r="E2" s="17" t="n"/>
@@ -2189,7 +2267,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_1</t>
+          <t>RmediumCmany_1</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -2201,31 +2279,31 @@
         <v>1</v>
       </c>
       <c r="D3" s="12" t="n">
-        <v>63.10821947203578</v>
+        <v>73.05906345584502</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>63.10821947203578</v>
+        <v>73.05906345584502</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>63.10821947203578</v>
+        <v>73.05906345584502</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="H3" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="J3" s="13" t="n">
-        <v>0.04421430324507714</v>
+        <v>0.02283372053149575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>RmediumCfew_1</t>
+          <t>RmediumCmany_1</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -2237,31 +2315,31 @@
         <v>1</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>62.9692177532143</v>
+        <v>76.41137761636904</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>62.9692177532143</v>
+        <v>76.41137761636904</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>62.9692177532143</v>
+        <v>76.41137761636904</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="H4" s="17" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>0.04191432419031456</v>
+        <v>0.06976643227192904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_1</t>
+          <t>RmediumCmany_1</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2273,31 +2351,31 @@
         <v>1</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>68.01790670547619</v>
+        <v>78.64211741666665</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>68.01790670547619</v>
+        <v>78.64211741666665</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>68.01790670547619</v>
+        <v>78.64211741666665</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>60.43608029110121</v>
+        <v>71.42809431222241</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0.1254519879160886</v>
+        <v>0.1009969980846852</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>RmediumCfew_2</t>
+          <t>RmediumCmany_2</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -2309,31 +2387,31 @@
         <v>1</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>53.69313401002289</v>
+        <v>54.66108585110236</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>53.69313401002289</v>
+        <v>54.66108585110236</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>53.69313401002289</v>
+        <v>54.66108585110236</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0.0428711525821091</v>
+        <v>0.01896905248707976</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_2</t>
+          <t>RmediumCmany_2</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2345,319 +2423,319 @@
         <v>1</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>53.39816867726203</v>
+        <v>57.38998875480632</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>53.39816867726203</v>
+        <v>57.38998875480632</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>53.39816867726203</v>
+        <v>57.38998875480632</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>51.48587519856191</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>0.03714209909659912</v>
+        <v>0.06984011666043043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>RmediumCfew_3</t>
+          <t>RmediumCmany_2</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>63.11641118745051</v>
+        <v>59.10586954714285</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>63.11641118745051</v>
+        <v>59.10586954714285</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>63.11641118745051</v>
+        <v>59.10586954714285</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>60.63537464247023</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>60.63537464247023</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>60.63537464247023</v>
+        <v>53.64351912129878</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.04091731204118775</v>
+        <v>0.101826847218815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>RmediumCfew_3</t>
+          <t>RmediumCmany_3</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>63.12365596635378</v>
+        <v>63.91878390299888</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>63.12365596635378</v>
+        <v>63.91878390299888</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>63.12365596635378</v>
+        <v>63.91878390299888</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>60.63537464247023</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>60.63537464247023</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>60.63537464247023</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.04103679310230082</v>
+        <v>0.01799381756829576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_3</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>36.98859933999925</v>
+        <v>66.969462261356</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>36.86501604614607</v>
+        <v>66.969462261356</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>37.11218263385243</v>
+        <v>66.969462261356</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>0.06203162512614268</v>
+        <v>0.06658003148797653</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_3</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>35.96842184845237</v>
+        <v>71.54532548023808</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>35.96842184845237</v>
+        <v>71.54532548023808</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>35.96842184845237</v>
+        <v>71.54532548023808</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>34.8281524437711</v>
+        <v>62.78897062035512</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0.03273987635497474</v>
+        <v>0.1394568946324515</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_1</t>
+          <t>RmediumCmany_4</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>39.6625499595238</v>
+        <v>59.60065254168538</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>39.6625499595238</v>
+        <v>59.60065254168538</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>39.6625499595238</v>
+        <v>59.60065254168538</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>34.8281524437711</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>34.8281524437711</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>34.8281524437711</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.1388071768537731</v>
+        <v>0.02549604700369947</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_10</t>
+          <t>RmediumCmany_4</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>34.30662940714284</v>
+        <v>62.25175325416657</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>34.30662940714284</v>
+        <v>62.25175325416657</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>34.30662940714284</v>
+        <v>62.25175325416657</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>30.79847871857142</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>30.79847871857142</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>30.79847871857142</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.113906622487039</v>
+        <v>0.07111120698800777</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_2</t>
+          <t>RmediumCmany_4</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>greedy</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>31.75477415523805</v>
+        <v>64.91336019095237</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>31.75477415523805</v>
+        <v>64.91336019095237</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>31.75477415523805</v>
+        <v>64.91336019095237</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>30.61323638288689</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>30.61323638288689</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>30.61323638288689</v>
+        <v>58.11885157024928</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>0.0372890261608957</v>
+        <v>0.1169071383403104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_2</t>
+          <t>RshortCmedium_1</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>33.87595654499999</v>
+        <v>37.157255159599</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>33.87595654499999</v>
+        <v>37.157255159599</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>33.87595654499999</v>
+        <v>37.157255159599</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>30.61323638288689</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>30.61323638288689</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>30.61323638288689</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.1065787400360256</v>
+        <v>0.0407901300186585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_3</t>
+          <t>RshortCmedium_1</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -2669,31 +2747,31 @@
         <v>1</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>35.78658326035708</v>
+        <v>38.12381854774306</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>35.78658326035708</v>
+        <v>38.12381854774306</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>35.78658326035708</v>
+        <v>38.12381854774306</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>0.03289857213907026</v>
+        <v>0.06786397145545948</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_3</t>
+          <t>RshortCmedium_1</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2705,103 +2783,103 @@
         <v>1</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>38.58447148000001</v>
+        <v>39.54358346047619</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>38.58447148000001</v>
+        <v>39.54358346047619</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>38.58447148000001</v>
+        <v>39.54358346047619</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>34.64675450779764</v>
+        <v>35.70100646413016</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>0.1136532707938386</v>
+        <v>0.1076321755860519</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_4</t>
+          <t>RshortCmedium_2</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>34.0275978452381</v>
+        <v>32.15800254512007</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>34.0275978452381</v>
+        <v>32.15800254512007</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>34.0275978452381</v>
+        <v>32.15800254512007</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>31.64735112160713</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>31.64735112160713</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>31.64735112160713</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>0.07521156239853068</v>
+        <v>0.01463328683049328</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_5</t>
+          <t>RshortCmedium_2</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>35.81904773809524</v>
+        <v>33.78295101238334</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>35.81904773809524</v>
+        <v>33.78295101238334</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>35.81904773809524</v>
+        <v>33.78295101238334</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>32.32325378330357</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>32.32325378330357</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>32.32325378330357</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0.1081510536726166</v>
+        <v>0.06590285190861717</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_6</t>
+          <t>RshortCmedium_2</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
@@ -2813,103 +2891,103 @@
         <v>1</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>34.70600726309525</v>
+        <v>34.44657884523808</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>34.70600726309525</v>
+        <v>34.44657884523808</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>34.70600726309525</v>
+        <v>34.44657884523808</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>31.95230189241174</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>31.95230189241174</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>31.95230189241174</v>
+        <v>31.69421204933566</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>0.08618175241194394</v>
+        <v>0.08684130691174909</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_7</t>
+          <t>RshortCmedium_3</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>34.33002832380952</v>
+        <v>36.31502266666667</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>34.33002832380952</v>
+        <v>36.31502266666667</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>34.33002832380952</v>
+        <v>36.31502266666667</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>31.0660137785119</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>31.0660137785119</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>31.0660137785119</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.1050670539377444</v>
+        <v>0.01256398059417058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>RshortCfew_8</t>
+          <t>RshortCmedium_3</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>greedy</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>34.47965599142857</v>
+        <v>38.26393734589607</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>34.47965599142857</v>
+        <v>38.26393734589607</v>
       </c>
       <c r="F22" s="17" t="n">
-        <v>34.47965599142857</v>
+        <v>38.26393734589607</v>
       </c>
       <c r="G22" s="17" t="n">
-        <v>32.43163137910714</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>32.43163137910714</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>32.43163137910714</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>0.06314898527247068</v>
+        <v>0.06690515018540721</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>RshortCfew_9</t>
+          <t>RshortCmedium_3</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2921,25 +2999,133 @@
         <v>1</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>38.67555929238095</v>
+        <v>39.62859034047619</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>38.67555929238095</v>
+        <v>39.62859034047619</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>38.67555929238095</v>
+        <v>39.62859034047619</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>34.89256813824403</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>34.89256813824403</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>34.89256813824403</v>
+        <v>35.86442275514984</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0.1084182493861942</v>
+        <v>0.1049554766578766</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>33.63751991845975</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>33.63751991845975</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>33.63751991845975</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0.0152859292305287</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>35.33904522678572</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>35.33904522678572</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>35.33904522678572</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>0.06664330361367843</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>RshortCmedium_4</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>greedy</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>35.46977987</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>35.46977987</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>35.46977987</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>33.131080565603</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>0.07058928548273984</v>
       </c>
     </row>
   </sheetData>
